--- a/Result/profitability/1805.xlsx
+++ b/Result/profitability/1805.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="N2" t="n">
-        <v>29.98875</v>
+        <v>44.64125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22875</v>
+        <v>-0.05374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>34.32375</v>
+        <v>40.9075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08374999999999999</v>
+        <v>-0.1225</v>
       </c>
       <c r="N4" t="n">
-        <v>27.37375</v>
+        <v>33.96</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3125</v>
+        <v>-0.31375</v>
       </c>
       <c r="N5" t="n">
-        <v>16.89</v>
+        <v>28.875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>-0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.39125</v>
+        <v>-0.3925000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>2.6075</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.435</v>
+        <v>-0.4625</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.39625</v>
+        <v>-2.615</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.48875</v>
+        <v>-0.51625</v>
       </c>
       <c r="N8" t="n">
-        <v>-15.27125</v>
+        <v>-7.185</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.02</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5037499999999999</v>
+        <v>-0.50375</v>
       </c>
       <c r="N9" t="n">
         <v>-17.6225</v>
@@ -2026,7 +2026,7 @@
         <v>-0.54</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.38125</v>
+        <v>-0.3812500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-11.255</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3163.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.832058906825262</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>23.27184466019417</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
